--- a/analyses/2026-08-20-analyse-complete-salve-trendtrack.xlsx
+++ b/analyses/2026-08-20-analyse-complete-salve-trendtrack.xlsx
@@ -45,7 +45,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +72,11 @@
         <fgColor rgb="00BF8F00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00833C0C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -85,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -93,6 +98,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -536,6 +545,11 @@
           <t>Motifs</t>
         </is>
       </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>Sourcing PUR AE</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -636,6 +650,11 @@
           <t>Saisonnalité été marquée (Q4 faible relatif) | Bande 50–400 € + enseignes non dominantes + au moins 1 preuve e-com/drop</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -786,6 +805,11 @@
           <t>Bande 50–400 € + enseignes non dominantes + au moins 1 preuve e-com/drop</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>AUCUNE OFFRE EXPLOITABLE (batardeau porte) / OFFRE TROUVÉE (sacs)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -836,6 +860,11 @@
           <t>Socle + bosse Q4 (OK UNIVERS / noter PUR) | Bande 50–400 € + enseignes non dominantes + au moins 1 preuve e-com/drop</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -886,6 +915,11 @@
           <t>Socle + bosse Q4 (OK UNIVERS / noter PUR) | Bande 50–400 € + enseignes non dominantes + au moins 1 preuve e-com/drop</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -934,6 +968,11 @@
       <c r="L9" t="inlineStr">
         <is>
           <t>Socle + bosse Q4 (OK UNIVERS / noter PUR) | Bande 50–400 € + enseignes non dominantes + au moins 1 preuve e-com/drop</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1407,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -1540,7 +1578,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -1616,7 +1653,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -1654,7 +1690,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -1692,7 +1727,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -1730,7 +1764,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>non</t>
@@ -1741,7 +1774,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1767,7 +1799,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -1808,7 +1839,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -1849,7 +1879,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -1890,7 +1919,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>non</t>
@@ -1931,7 +1959,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -1972,7 +1999,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2013,7 +2039,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>non</t>
@@ -2054,7 +2079,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2095,7 +2119,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>non</t>
@@ -2136,7 +2159,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>non</t>
@@ -2177,7 +2199,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2218,7 +2239,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2259,7 +2279,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>non</t>
@@ -2345,7 +2364,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>non</t>
@@ -2386,7 +2404,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2427,7 +2444,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2468,7 +2484,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2509,7 +2524,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2550,7 +2564,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2591,7 +2604,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2632,7 +2644,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2673,7 +2684,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2714,7 +2724,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2755,7 +2764,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2796,7 +2804,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2837,7 +2844,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2878,7 +2884,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -2964,7 +2969,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -3005,7 +3009,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -3046,7 +3049,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>non</t>
@@ -3087,7 +3089,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -3128,7 +3129,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -3169,7 +3169,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -3210,7 +3209,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -3227,7 +3225,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -3402,7 +3399,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -3535,7 +3531,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -3611,7 +3606,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -3649,7 +3643,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>non</t>
@@ -3660,7 +3653,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3683,7 +3675,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>non</t>
@@ -3694,7 +3685,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3717,7 +3707,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
@@ -3728,7 +3717,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3751,7 +3739,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>non</t>
@@ -3762,7 +3749,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3785,7 +3771,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>non</t>
@@ -3796,7 +3781,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3822,7 +3806,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>non</t>
@@ -3863,7 +3846,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -3904,7 +3886,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -3945,7 +3926,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>non</t>
@@ -3986,7 +3966,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>non</t>
@@ -4027,7 +4006,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>non</t>
@@ -4158,7 +4136,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -4199,7 +4176,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -4240,7 +4216,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>non</t>
@@ -4281,7 +4256,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>non</t>
@@ -4322,7 +4296,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>non</t>
@@ -4363,7 +4336,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -4404,7 +4376,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -4445,7 +4416,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -4486,7 +4456,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>non</t>
@@ -4527,7 +4496,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>non</t>
@@ -4613,7 +4581,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -4744,7 +4711,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>non</t>
@@ -4785,7 +4751,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>non</t>
@@ -4826,7 +4791,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -4867,7 +4831,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>non</t>
@@ -4908,7 +4871,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>non</t>
@@ -4994,7 +4956,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>non</t>
@@ -5035,7 +4996,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -5076,7 +5036,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>non</t>
@@ -5117,7 +5076,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>non</t>
@@ -5158,7 +5116,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -5199,7 +5156,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>non</t>
@@ -5285,7 +5241,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>non</t>
@@ -5326,7 +5281,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>non</t>
@@ -5367,7 +5321,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>non</t>
@@ -5408,7 +5361,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -5425,7 +5377,6 @@
         </is>
       </c>
     </row>
-    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
@@ -5600,7 +5551,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -5733,7 +5683,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -5809,7 +5758,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>non</t>
@@ -5820,7 +5768,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5843,7 +5790,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>non</t>
@@ -5854,7 +5800,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5877,7 +5822,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>non</t>
@@ -5888,7 +5832,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5911,7 +5854,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
@@ -5922,7 +5864,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5945,7 +5886,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>non</t>
@@ -5956,7 +5896,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5994,7 +5933,6 @@
           <t>Grande enseigne / marketplace</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6017,7 +5955,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>non</t>
@@ -6028,7 +5965,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6054,7 +5990,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6095,7 +6030,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6136,7 +6070,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6177,7 +6110,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>non</t>
@@ -6218,7 +6150,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6259,7 +6190,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6300,7 +6230,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6341,7 +6270,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>non</t>
@@ -6427,7 +6355,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6468,7 +6395,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>non</t>
@@ -6554,7 +6480,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6595,7 +6520,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6636,7 +6560,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6677,7 +6600,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6763,7 +6685,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6804,7 +6725,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6980,7 +6900,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -6997,7 +6916,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
@@ -7172,7 +7090,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -7305,7 +7222,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -7381,7 +7297,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -7419,7 +7334,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>non</t>
@@ -7430,7 +7344,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7453,7 +7366,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>non</t>
@@ -7464,7 +7376,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7487,7 +7398,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
@@ -7498,7 +7408,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7569,7 +7478,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>non</t>
@@ -7700,7 +7608,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>non</t>
@@ -7921,7 +7828,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>non</t>
@@ -8052,7 +7958,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>non</t>
@@ -8249,7 +8154,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -8424,7 +8328,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -8557,7 +8460,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -8633,7 +8535,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -8671,7 +8572,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>non</t>
@@ -8682,7 +8582,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8705,7 +8604,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>non</t>
@@ -8716,7 +8614,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8742,7 +8639,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
@@ -8783,7 +8679,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>non</t>
@@ -8824,7 +8719,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>non</t>
@@ -8865,7 +8759,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>non</t>
@@ -8906,7 +8799,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>non</t>
@@ -8947,7 +8839,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>non</t>
@@ -8988,7 +8879,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -9029,7 +8919,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>non</t>
@@ -9070,7 +8959,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -9111,7 +8999,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>non</t>
@@ -9152,7 +9039,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>non</t>
@@ -9193,7 +9079,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>non</t>
@@ -9234,7 +9119,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>non</t>
@@ -9275,7 +9159,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>non</t>
@@ -9316,7 +9199,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>non</t>
@@ -9354,7 +9236,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>non</t>
@@ -9395,7 +9276,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>non</t>
@@ -9436,7 +9316,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>non</t>
@@ -9477,7 +9356,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>non</t>
@@ -9518,7 +9396,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -9559,7 +9436,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>non</t>
@@ -9600,7 +9476,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>non</t>
@@ -9686,7 +9561,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>non</t>
@@ -9727,7 +9601,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>non</t>
@@ -9768,7 +9641,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>non</t>
@@ -9809,7 +9681,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>non</t>
@@ -9850,7 +9721,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>non</t>
@@ -9867,7 +9737,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -10042,7 +9911,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -10175,7 +10043,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -10251,7 +10118,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -10304,7 +10170,6 @@
           <t>Grande enseigne / marketplace</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10327,7 +10192,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>non</t>
@@ -10338,7 +10202,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10376,7 +10239,6 @@
           <t>Grande enseigne / marketplace</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10399,7 +10261,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>non</t>
@@ -10410,7 +10271,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10433,7 +10293,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>non</t>
@@ -10444,7 +10303,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10467,7 +10325,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>non</t>
@@ -10478,7 +10335,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10501,7 +10357,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>non</t>
@@ -10512,7 +10367,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10550,7 +10404,6 @@
           <t>Grande enseigne / marketplace</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10573,7 +10426,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>non</t>
@@ -10584,7 +10436,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10610,7 +10461,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -10651,7 +10501,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -10692,7 +10541,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -10733,7 +10581,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -10774,7 +10621,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>non</t>
@@ -10815,7 +10661,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -10856,7 +10701,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -10918,7 +10762,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
@@ -11183,7 +11026,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -11261,7 +11103,6 @@
       <c r="F13" t="n">
         <v>52</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Q4≈75 vs hors-Q4≈63; été≈52 (52 sem.)</t>
@@ -11296,7 +11137,6 @@
       <c r="F14" t="n">
         <v>48</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Q4≈80 vs hors-Q4≈58; été≈48 (52 sem.)</t>
@@ -11308,7 +11148,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -11384,7 +11223,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>non</t>
@@ -11395,7 +11233,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11421,7 +11258,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>non</t>
@@ -11462,7 +11298,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>non</t>
@@ -11503,7 +11338,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
@@ -11544,7 +11378,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>non</t>
@@ -11585,7 +11418,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>non</t>
@@ -11626,7 +11458,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>non</t>
@@ -11667,7 +11498,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>non</t>
@@ -11708,7 +11538,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>non</t>
@@ -11749,7 +11578,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>non</t>
@@ -11790,7 +11618,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>non</t>
@@ -11831,7 +11658,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>non</t>
@@ -11869,7 +11695,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>non</t>
@@ -11910,7 +11735,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>non</t>
@@ -11951,7 +11775,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>non</t>
@@ -11992,7 +11815,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>non</t>
@@ -12033,7 +11855,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>non</t>
@@ -12074,7 +11895,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>non</t>
@@ -12115,7 +11935,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>non</t>
@@ -12156,7 +11975,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>non</t>
@@ -12242,7 +12060,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>non</t>
@@ -12283,7 +12100,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>non</t>
@@ -12324,7 +12140,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>non</t>
@@ -12365,7 +12180,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>non</t>
@@ -12406,7 +12220,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>non</t>
@@ -12447,7 +12260,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>non</t>
@@ -12464,7 +12276,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -12519,12 +12330,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -12639,7 +12450,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -12717,7 +12527,6 @@
       <c r="F13" t="n">
         <v>52</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Q4≈16 vs hors-Q4≈29; été≈52 (52 sem.)</t>
@@ -12752,7 +12561,6 @@
       <c r="F14" t="n">
         <v>38</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Q4≈0 vs hors-Q4≈22; été≈38 (52 sem.)</t>
@@ -12764,7 +12572,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -12843,7 +12650,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -12884,7 +12690,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>non</t>
@@ -12925,7 +12730,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -12966,7 +12770,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
@@ -13007,7 +12810,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>non</t>
@@ -13048,7 +12850,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>non</t>
@@ -13089,7 +12890,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>non</t>
@@ -13130,7 +12930,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>non</t>
@@ -13171,7 +12970,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>non</t>
@@ -13212,7 +13010,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>non</t>
@@ -13298,7 +13095,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>non</t>
@@ -13384,7 +13180,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>non</t>
@@ -13425,7 +13220,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>non</t>
@@ -13466,7 +13260,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>non</t>
@@ -13507,7 +13300,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>non</t>
@@ -13548,7 +13340,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>non</t>
@@ -13589,7 +13380,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -13630,7 +13420,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>non</t>
@@ -13671,7 +13460,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>non</t>
@@ -13757,7 +13545,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>non</t>
@@ -13843,7 +13630,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>non</t>
@@ -13929,7 +13715,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>non</t>
@@ -13970,7 +13755,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>non</t>
@@ -14056,7 +13840,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -14097,7 +13880,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>non</t>
@@ -14138,7 +13920,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>non</t>
@@ -14224,7 +14005,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>non</t>
@@ -14265,7 +14045,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>non</t>
@@ -14282,7 +14061,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -14323,6 +14101,372 @@
       <c r="B57" t="inlineStr">
         <is>
           <t>Shopify + PDP type drop + pas d'entreprise établie (mémoire 06/08/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>--- SOURCING ALIEXPRESS PUR — 2026-08-20 — FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Synthèse</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Caches acier Local+/FR (Fedex gratuit 3–10 j) — preuve sociale faible (1–6 vendus). Housses souples CN abondantes mais ≠ produit marché décoratif 140–250€.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Rappel</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Aucun achat / contact vendeur. GO fournisseur n’existe pas sans commande test. Prix/stocks dynamiques — reconfirmer au panier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Statut sourcing</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Confiance</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>URL AliExpress</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Titre / variante</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>Commandes</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Prix variante €</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Expédié depuis</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>Transporteur / frais</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>Délai FR</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>Coût rendu estim.</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>Réserves</t>
+        </is>
+      </c>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005012807933180.html</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Cache clim acier anthracite 110x50x80</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>~242–255€</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>France (Local+)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Fedex_FR gratuit</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>3–10 j</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>~255€</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Électrique non; colis volumineux; peu de ventes</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>acier rigid FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005012807871444.html</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Cache clim acier argenté 110x50x105</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>~208–231€</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>France (Local+)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Fedex_FR gratuit</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>3–10 j</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>~231€</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Peu de ventes</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>acier rigid FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005012624984391.html</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Cache clim acier argenté 110x50x105</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>207.46€</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>France (Local+)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Fedex_FR gratuit</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>3–10 j</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>207€</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Peu de ventes</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>acier rigid FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>OFFRE TROUVÉE (alt.)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005012308542554.html</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Housse souple clim extérieur</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2000+</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>3.89€</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Chine</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>≠ cache décoratif marché; low-ticket</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>rejet produit</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14601,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -14535,7 +14678,6 @@
       <c r="F13" t="n">
         <v>39</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Q4≈4 vs hors-Q4≈25; été≈39 (52 sem.)</t>
@@ -14570,7 +14712,6 @@
       <c r="F14" t="n">
         <v>32</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Q4≈3 vs hors-Q4≈17; été≈32 (52 sem.)</t>
@@ -14582,7 +14723,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -14658,7 +14798,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -14696,7 +14835,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>non</t>
@@ -14707,7 +14845,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14730,7 +14867,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>non</t>
@@ -14741,7 +14877,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14764,7 +14899,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
@@ -14775,7 +14909,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14798,7 +14931,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>non</t>
@@ -14809,7 +14941,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14835,7 +14966,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>non</t>
@@ -14876,7 +15006,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>non</t>
@@ -14917,7 +15046,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>non</t>
@@ -14958,7 +15086,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -14999,7 +15126,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>non</t>
@@ -15085,7 +15211,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>non</t>
@@ -15126,7 +15251,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>non</t>
@@ -15167,7 +15291,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>non</t>
@@ -15208,7 +15331,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -15249,7 +15371,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>non</t>
@@ -15290,7 +15411,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -15331,7 +15451,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>non</t>
@@ -15372,7 +15491,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>non</t>
@@ -15458,7 +15576,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>non</t>
@@ -15544,7 +15661,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>non</t>
@@ -15585,7 +15701,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>non</t>
@@ -15671,7 +15786,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>non</t>
@@ -15712,7 +15826,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>non</t>
@@ -15753,7 +15866,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>non</t>
@@ -15794,7 +15906,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>non</t>
@@ -15835,7 +15946,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>non</t>
@@ -15876,7 +15986,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>non</t>
@@ -15917,7 +16026,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>non</t>
@@ -15958,7 +16066,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>non</t>
@@ -15999,7 +16106,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>non</t>
@@ -16040,7 +16146,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>non</t>
@@ -16057,7 +16162,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -16232,7 +16336,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -16310,7 +16413,6 @@
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Q4≈0 vs hors-Q4≈0; été≈0 (52 sem.)</t>
@@ -16345,7 +16447,6 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Q4≈0 vs hors-Q4≈0; été≈0 (52 sem.)</t>
@@ -16357,7 +16458,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -16433,7 +16533,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -16471,7 +16570,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>non</t>
@@ -16482,7 +16580,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16508,7 +16605,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>non</t>
@@ -16549,7 +16645,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
@@ -16680,7 +16775,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>non</t>
@@ -16901,7 +16995,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>non</t>
@@ -16942,7 +17035,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>non</t>
@@ -17118,7 +17210,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>non</t>
@@ -17429,7 +17520,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>non</t>
@@ -17515,7 +17605,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>non</t>
@@ -17691,7 +17780,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>non</t>
@@ -17822,7 +17910,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -18043,7 +18130,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>non</t>
@@ -18129,7 +18215,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>non</t>
@@ -18146,7 +18231,6 @@
         </is>
       </c>
     </row>
-    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
@@ -18201,12 +18285,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -18321,7 +18405,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -18399,7 +18482,6 @@
       <c r="F13" t="n">
         <v>20</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Q4≈18 vs hors-Q4≈20; été≈20 (52 sem.)</t>
@@ -18434,7 +18516,6 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Q4≈0 vs hors-Q4≈0; été≈0 (52 sem.)</t>
@@ -18446,7 +18527,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -18522,7 +18602,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>non</t>
@@ -18533,7 +18612,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18556,7 +18634,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>non</t>
@@ -18567,7 +18644,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18590,7 +18666,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>non</t>
@@ -18601,7 +18676,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -18624,7 +18698,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
@@ -18635,7 +18708,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -18658,7 +18730,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>non</t>
@@ -18669,7 +18740,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18692,7 +18762,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>non</t>
@@ -18703,7 +18772,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -18729,7 +18797,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>non</t>
@@ -18770,7 +18837,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>non</t>
@@ -18811,7 +18877,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>non</t>
@@ -18852,7 +18917,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>non</t>
@@ -18938,7 +19002,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>non</t>
@@ -18979,7 +19042,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>non</t>
@@ -19020,7 +19082,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>non</t>
@@ -19061,7 +19122,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -19102,7 +19162,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>non</t>
@@ -19278,7 +19337,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>non</t>
@@ -19319,7 +19377,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>non</t>
@@ -19405,7 +19462,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>non</t>
@@ -19446,7 +19502,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>non</t>
@@ -19487,7 +19542,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>non</t>
@@ -19573,7 +19627,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>non</t>
@@ -19614,7 +19667,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -19745,7 +19797,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>non</t>
@@ -19786,7 +19837,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>non</t>
@@ -19872,7 +19922,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>non</t>
@@ -19913,7 +19962,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>non</t>
@@ -19999,7 +20047,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>non</t>
@@ -20217,7 +20264,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>non</t>
@@ -20258,7 +20304,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>non</t>
@@ -20299,7 +20344,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>non</t>
@@ -20316,7 +20360,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -20357,6 +20400,372 @@
       <c r="B66" t="inlineStr">
         <is>
           <t>Shopify + PDP type drop + pas d'entreprise établie (mémoire 06/08/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>--- SOURCING ALIEXPRESS PUR — 2026-08-20 — AUCUNE OFFRE EXPLOITABLE (batardeau porte) / OFFRE TROUVÉE (sacs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Synthèse</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pas de batardeau porte dimensionnable honnête (confirmé phase4 03/08). Sacs anti-inondation / water-activated bags CN 4–10€ = adjacent, ticket hors bande boutique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Rappel</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Aucun achat / contact vendeur. GO fournisseur n’existe pas sans commande test. Prix/stocks dynamiques — reconfirmer au panier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Statut sourcing</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Confiance</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>URL AliExpress</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Titre / variante</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Commandes</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>Prix variante €</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Expédié depuis</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>Transporteur / frais</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>Délai FR</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>Coût rendu estim.</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>Réserves</t>
+        </is>
+      </c>
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>OFFRE TROUVÉE</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005011653733893.html</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sacs de sable inondation réutilisables</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1000+</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>4.49€</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Chine</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Cainiao ~1,99€</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>5–9 j</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>~6.5€</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Pas un batardeau porte; low-ticket</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>OFFRE TROUVÉE</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005008136590249.html</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sacs sable activés par eau</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>7.29€</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Chine</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Cainiao ~1,99€</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>7–13 j</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>~9€</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>OFFRE TROUVÉE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005010234957093.html</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Barrière absorbe-eau maison</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>7.79€</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Chine</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Cainiao ~1,99€</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>7–13 j</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>~10€</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Pas dimensions porte sélectionnables</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>barre/sac</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AUCUNE OFFRE EXPLOITABLE</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Batardeau porte largeur/hauteur sélectionnables</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>809–2052€ historique phase4</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Aucun SKU gates produit</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>batardeau</t>
         </is>
       </c>
     </row>
@@ -20371,12 +20780,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -20491,7 +20900,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -20569,7 +20977,6 @@
       <c r="F13" t="n">
         <v>25</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Q4≈68 vs hors-Q4≈36; été≈25 (52 sem.)</t>
@@ -20604,7 +21011,6 @@
       <c r="F14" t="n">
         <v>25</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Q4≈62 vs hors-Q4≈31; été≈25 (52 sem.)</t>
@@ -20616,7 +21022,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -20692,7 +21097,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>non</t>
@@ -20703,7 +21107,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20741,7 +21144,6 @@
           <t>Grande enseigne / marketplace</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -20764,7 +21166,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>non</t>
@@ -20775,7 +21176,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -20801,7 +21201,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
@@ -20887,7 +21286,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>non</t>
@@ -20928,7 +21326,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>non</t>
@@ -20969,7 +21366,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>non</t>
@@ -21055,7 +21451,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>non</t>
@@ -21141,7 +21536,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>non</t>
@@ -21227,7 +21621,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>non</t>
@@ -21313,7 +21706,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>non</t>
@@ -21354,7 +21746,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>non</t>
@@ -21395,7 +21786,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>non</t>
@@ -21436,7 +21826,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>non</t>
@@ -21477,7 +21866,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>non</t>
@@ -21518,7 +21906,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>non</t>
@@ -21649,7 +22036,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>non</t>
@@ -21735,7 +22121,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -21776,7 +22161,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>non</t>
@@ -21817,7 +22201,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -21858,7 +22241,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>non</t>
@@ -21944,7 +22326,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>non</t>
@@ -21985,7 +22366,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>non</t>
@@ -22023,7 +22403,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>non</t>
@@ -22109,7 +22488,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>non</t>
@@ -22150,7 +22528,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>non</t>
@@ -22236,7 +22613,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>non</t>
@@ -22277,7 +22653,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>non</t>
@@ -22318,7 +22693,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -22359,7 +22733,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>non</t>
@@ -22376,7 +22749,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -22417,6 +22789,439 @@
       <c r="B63" t="inlineStr">
         <is>
           <t>Shopify + PDP type drop + pas d'entreprise établie (mémoire 06/08/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>--- SOURCING ALIEXPRESS PUR — 2026-08-20 — FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Synthèse</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Rails électriques 220V stockés, plusieurs depuis Allemagne (DPD 4–10 j, port souvent inclus). Vigilance CE/électrique. Variantes Local+ FR souvent OOS au moment du relevé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Rappel</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Aucun achat / contact vendeur. GO fournisseur n’existe pas sans commande test. Prix/stocks dynamiques — reconfirmer au panier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Statut sourcing</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Confiance</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>URL AliExpress</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Titre / variante</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Commandes</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Prix variante €</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Expédié depuis</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>Transporteur / frais</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>Délai FR</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>Coût rendu estim.</t>
+        </is>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>Réserves</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005009174278960.html</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Porte-serviettes chauffant électrique (White-D-4360)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>47.19€</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>DPD DE (fee null)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>4–10 j</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>~47€</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Stock faible (5); électrique CE à vérifier</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>rail DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005009157113759.html</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sèche-serviettes électrique Black 96x49</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>194+</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>82.69€</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>DPD DE Pan-EU</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>4–10 j</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>~83€</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Stock 66; électrique</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>rail DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005008858377822.html</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Sèche-serviettes Black 4896</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>132+</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>80.69€</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>DPD DE Pan-EU</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>4–10 j</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>~81€</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Stock 10</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>rail DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>OFFRE TROUVÉE</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005011910646034.html</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sèche-serviettes vertical doré 2 rods</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>116.39€</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Chine</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>UPS Express 69,79€</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>3–13 j</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>~186€</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Fret élevé; WiFi option</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>rail CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>OFFRE TROUVÉE (OOS sample)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005009252824844.html</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Porte-serviettes chauffant noir affichage</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>~40–47€</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Local+ listé</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>SKU sample out of stock à l’exact</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>OOS</t>
         </is>
       </c>
     </row>
@@ -22431,12 +23236,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -22551,7 +23356,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -22629,7 +23433,6 @@
       <c r="F13" t="n">
         <v>21</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Q4≈54 vs hors-Q4≈21; été≈21 (52 sem.)</t>
@@ -22664,7 +23467,6 @@
       <c r="F14" t="n">
         <v>19</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Q4≈62 vs hors-Q4≈24; été≈19 (52 sem.)</t>
@@ -22676,7 +23478,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -22752,7 +23553,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>non</t>
@@ -22763,7 +23563,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22786,7 +23585,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>non</t>
@@ -22797,7 +23595,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -22820,7 +23617,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>non</t>
@@ -22831,7 +23627,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -22854,7 +23649,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
@@ -22865,7 +23659,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -22888,7 +23681,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>non</t>
@@ -22899,7 +23691,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -22922,7 +23713,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>non</t>
@@ -22933,7 +23723,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22959,7 +23748,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>non</t>
@@ -23000,7 +23788,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>non</t>
@@ -23041,7 +23828,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -23082,7 +23868,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>non</t>
@@ -23123,7 +23908,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>non</t>
@@ -23164,7 +23948,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>non</t>
@@ -23205,7 +23988,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>non</t>
@@ -23246,7 +24028,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -23287,7 +24068,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>non</t>
@@ -23328,7 +24108,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>non</t>
@@ -23369,7 +24148,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>non</t>
@@ -23410,7 +24188,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -23451,7 +24228,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -23492,7 +24268,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>non</t>
@@ -23533,7 +24308,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>non</t>
@@ -23574,7 +24348,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -23615,7 +24388,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>non</t>
@@ -23656,7 +24428,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>non</t>
@@ -23697,7 +24468,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>non</t>
@@ -23738,7 +24508,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>non</t>
@@ -23779,7 +24548,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -23820,7 +24588,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>non</t>
@@ -23861,7 +24628,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -23902,7 +24668,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>non</t>
@@ -23943,7 +24708,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>non</t>
@@ -24029,7 +24793,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -24070,7 +24833,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>non</t>
@@ -24111,7 +24873,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>non</t>
@@ -24152,7 +24913,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -24169,7 +24929,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
@@ -24210,6 +24969,439 @@
       <c r="B58" t="inlineStr">
         <is>
           <t>Shopify + PDP type drop + pas d'entreprise établie (mémoire 06/08/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- SOURCING ALIEXPRESS PUR — 2026-08-20 — FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Synthèse</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Lampes cou LED très fournies CN (8–14€, 2k–10k cmd) — sous la médiane Shopping FR (~99€). Option DE Local ~55€ plus proche bande.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Rappel</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Aucun achat / contact vendeur. GO fournisseur n’existe pas sans commande test. Prix/stocks dynamiques — reconfirmer au panier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Statut sourcing</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Confiance</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>URL AliExpress</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Titre / variante</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Commandes</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>Prix variante €</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Expédié depuis</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>Transporteur / frais</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>Délai FR</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>Coût rendu estim.</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>Réserves</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005012302793728.html</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lampe lecture LED cou LQWELL (DE)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>54.61€</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>DHL DE gratuit</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>3–8 j</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>~55€</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Peu de ventes mais ship DE; mieux aligné prix</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>neck DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005006861962011.html</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Lampe lecture LED rechargeable cou</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>3000+</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>12–13€</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Chine</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Cainiao ~1,99€</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>5–9 j</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>~15€</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Low-ticket vs marché; ambiguous variant exact</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>neck CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005009720565039.html</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lampe lecture LED cou 2 niveaux</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2000+</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>13.69€</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Chine</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Cainiao 1,99€</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>5–9 j</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>~16€</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Low-ticket</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>neck CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005006120198988.html</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Lampe lecture cou flexible</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2000+</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>12.49€</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Chine</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Cainiao 1,99€</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>5–9 j</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>~14.5€</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Low-ticket</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>neck CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005007594151139.html</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Lampes lecture LED cou 3 couleurs</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2000+</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>9.29€</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Chine</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Cainiao 1,99€</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>5–11 j</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>~11€</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Low-ticket</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>neck CN</t>
         </is>
       </c>
     </row>
@@ -24224,12 +25416,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -24344,7 +25536,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -24422,7 +25613,6 @@
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Q4≈43 vs hors-Q4≈0; été≈0 (52 sem.)</t>
@@ -24457,7 +25647,6 @@
       <c r="F14" t="n">
         <v>6</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Q4≈38 vs hors-Q4≈19; été≈6 (52 sem.)</t>
@@ -24469,7 +25658,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -24545,7 +25733,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -24583,7 +25770,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>non</t>
@@ -24594,7 +25780,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24617,7 +25802,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>non</t>
@@ -24628,7 +25812,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -24651,7 +25834,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
@@ -24662,7 +25844,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24685,7 +25866,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>non</t>
@@ -24696,7 +25876,6 @@
           <t>Indépendant / marque</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -24722,7 +25901,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -24763,7 +25941,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -24804,7 +25981,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>non</t>
@@ -24845,7 +26021,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>non</t>
@@ -24886,7 +26061,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -24927,7 +26101,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>non</t>
@@ -24968,7 +26141,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -25009,7 +26181,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>non</t>
@@ -25050,7 +26221,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -25091,7 +26261,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>non</t>
@@ -25132,7 +26301,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -25173,7 +26341,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -25214,7 +26381,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>non</t>
@@ -25255,7 +26421,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>non</t>
@@ -25296,7 +26461,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>non</t>
@@ -25337,7 +26501,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>non</t>
@@ -25423,7 +26586,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -25464,7 +26626,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -25505,7 +26666,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>non</t>
@@ -25591,7 +26751,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>non</t>
@@ -25632,7 +26791,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>non</t>
@@ -25673,7 +26831,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>non</t>
@@ -25714,7 +26871,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>non</t>
@@ -25755,7 +26911,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>non</t>
@@ -25796,7 +26951,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>non</t>
@@ -25882,7 +27036,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>non</t>
@@ -25923,7 +27076,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>non</t>
@@ -25964,7 +27116,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>non</t>
@@ -26005,7 +27156,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>non</t>
@@ -26091,7 +27241,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>non</t>
@@ -26132,7 +27281,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>non</t>
@@ -26173,7 +27321,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>oui?</t>
@@ -26214,7 +27361,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>non</t>
@@ -26255,7 +27401,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>non</t>
@@ -26296,7 +27441,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>non</t>
@@ -26337,7 +27481,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>non</t>
@@ -26354,7 +27497,6 @@
         </is>
       </c>
     </row>
-    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
@@ -26395,6 +27537,372 @@
       <c r="B67" t="inlineStr">
         <is>
           <t>Shopify + PDP type drop + pas d'entreprise établie (mémoire 06/08/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>--- SOURCING ALIEXPRESS PUR — 2026-08-20 — FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Synthèse</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Panneaux / radiateurs IR muraux trouvés. Meilleur ship: DE 850W ~200€ port inclus. CN + fret lourd souvent. Vigilance électrique/CE renforcée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Rappel</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Aucun achat / contact vendeur. GO fournisseur n’existe pas sans commande test. Prix/stocks dynamiques — reconfirmer au panier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Statut sourcing</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Confiance</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>URL AliExpress</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Titre / variante</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Commandes</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>Prix variante €</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>Expédié depuis</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>Transporteur / frais</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>Délai FR</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>Coût rendu estim.</t>
+        </is>
+      </c>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>Réserves</t>
+        </is>
+      </c>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005010770201820.html</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Chauffage mural IR 850W (exp. Allemagne)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>199.52€</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Seller Shipping DE local</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>4–10 j</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>~200€</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Électrique CE; puissance/prise</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>panel DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005010290676230.html</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Panneau IR cristal carbone 180W blanc EU</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>99.39€</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Chine</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Premium 35,30€</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>7–11 j</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>~135€</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Fret; plug EU dispo</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>panel CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FOURNISSEUR À TESTER</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005007979961710.html</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Panneau IR mural 180W Pure white</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>108.69€</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Chine</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Premium 59,81€</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>7–11 j</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>~168€</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Fret élevé</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>panel CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>OFFRE TROUVÉE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://fr.aliexpress.com/item/1005008729022183.html</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Panneau lumière rouge IR 200W</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>92.39€</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Allemagne?</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>DHL DE listé</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>4–9 j</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>~92€</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Thérapie LED ≠ chauffage pièce</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>rejet usage</t>
         </is>
       </c>
     </row>
